--- a/data/monthly/【2025年8月】月次数値.xlsx
+++ b/data/monthly/【2025年8月】月次数値.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="96">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -218,6 +218,96 @@
   </si>
   <si>
     <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼ドキドキ💓はじめてのスポーツ体験！／...</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼2〜3歳のお子さまも大歓迎👶✨／...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【🦷アキュラデンタルクリニック🦷】...</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【せがわ歯科クリニック】です🦷✨...</t>
   </si>
 </sst>
 </file>
@@ -567,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -1459,7 +1549,7 @@
         <v>26.53304</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1533,7 +1623,7 @@
         <v>101.492063</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1607,7 +1697,7 @@
         <v>52.813084000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1681,7 +1771,7 @@
         <v>42.344262000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1903,7 +1993,7 @@
         <v>65.342466000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1975,6 +2065,1378 @@
       </c>
       <c r="Y21">
         <v>136.444444</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22">
+        <v>182</v>
+      </c>
+      <c r="G22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22">
+        <v>5034</v>
+      </c>
+      <c r="I22">
+        <v>1.6517679999999999</v>
+      </c>
+      <c r="J22">
+        <v>27.274725270000001</v>
+      </c>
+      <c r="K22">
+        <v>160</v>
+      </c>
+      <c r="L22" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22">
+        <v>4964</v>
+      </c>
+      <c r="N22" t="s">
+        <v>69</v>
+      </c>
+      <c r="O22">
+        <v>8315</v>
+      </c>
+      <c r="P22">
+        <v>596.99338499999999</v>
+      </c>
+      <c r="Q22">
+        <v>182</v>
+      </c>
+      <c r="S22">
+        <v>27.274725</v>
+      </c>
+      <c r="T22">
+        <v>2.188815</v>
+      </c>
+      <c r="U22">
+        <v>272</v>
+      </c>
+      <c r="V22">
+        <v>3.2711969999999999</v>
+      </c>
+      <c r="W22">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23">
+        <v>123</v>
+      </c>
+      <c r="G23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23">
+        <v>6222</v>
+      </c>
+      <c r="I23">
+        <v>1.2555449999999999</v>
+      </c>
+      <c r="J23">
+        <v>40.406504069999997</v>
+      </c>
+      <c r="K23">
+        <v>160</v>
+      </c>
+      <c r="L23" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23">
+        <v>4970</v>
+      </c>
+      <c r="N23" t="s">
+        <v>71</v>
+      </c>
+      <c r="O23">
+        <v>7812</v>
+      </c>
+      <c r="P23">
+        <v>636.20071700000005</v>
+      </c>
+      <c r="Q23">
+        <v>123</v>
+      </c>
+      <c r="S23">
+        <v>40.406503999999998</v>
+      </c>
+      <c r="T23">
+        <v>1.5745009999999999</v>
+      </c>
+      <c r="U23">
+        <v>135</v>
+      </c>
+      <c r="V23">
+        <v>1.728111</v>
+      </c>
+      <c r="W23">
+        <v>36.814815000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>247</v>
+      </c>
+      <c r="G24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24">
+        <v>5025</v>
+      </c>
+      <c r="I24">
+        <v>1.356816</v>
+      </c>
+      <c r="J24">
+        <v>20.07287449</v>
+      </c>
+      <c r="K24">
+        <v>160</v>
+      </c>
+      <c r="L24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M24">
+        <v>4958</v>
+      </c>
+      <c r="N24" t="s">
+        <v>71</v>
+      </c>
+      <c r="O24">
+        <v>6818</v>
+      </c>
+      <c r="P24">
+        <v>727.192725</v>
+      </c>
+      <c r="Q24">
+        <v>247</v>
+      </c>
+      <c r="S24">
+        <v>20.072873999999999</v>
+      </c>
+      <c r="T24">
+        <v>3.622763</v>
+      </c>
+      <c r="U24">
+        <v>333</v>
+      </c>
+      <c r="V24">
+        <v>4.8841299999999999</v>
+      </c>
+      <c r="W24">
+        <v>14.888889000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25">
+        <v>225</v>
+      </c>
+      <c r="G25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25">
+        <v>3521</v>
+      </c>
+      <c r="I25">
+        <v>1.3942060000000001</v>
+      </c>
+      <c r="J25">
+        <v>22.06666667</v>
+      </c>
+      <c r="K25">
+        <v>160</v>
+      </c>
+      <c r="L25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25">
+        <v>4965</v>
+      </c>
+      <c r="N25" t="s">
+        <v>74</v>
+      </c>
+      <c r="O25">
+        <v>4909</v>
+      </c>
+      <c r="P25">
+        <v>1011.407619</v>
+      </c>
+      <c r="Q25">
+        <v>225</v>
+      </c>
+      <c r="S25">
+        <v>22.066666999999999</v>
+      </c>
+      <c r="T25">
+        <v>4.583418</v>
+      </c>
+      <c r="U25">
+        <v>246</v>
+      </c>
+      <c r="V25">
+        <v>5.0112040000000002</v>
+      </c>
+      <c r="W25">
+        <v>20.182926999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26">
+        <v>150</v>
+      </c>
+      <c r="G26" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26">
+        <v>3651</v>
+      </c>
+      <c r="I26">
+        <v>1.7200770000000001</v>
+      </c>
+      <c r="J26">
+        <v>33.09333333</v>
+      </c>
+      <c r="K26">
+        <v>160</v>
+      </c>
+      <c r="L26" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26">
+        <v>4964</v>
+      </c>
+      <c r="N26" t="s">
+        <v>76</v>
+      </c>
+      <c r="O26">
+        <v>6280</v>
+      </c>
+      <c r="P26">
+        <v>790.44586000000004</v>
+      </c>
+      <c r="Q26">
+        <v>150</v>
+      </c>
+      <c r="S26">
+        <v>33.093333000000001</v>
+      </c>
+      <c r="T26">
+        <v>2.3885350000000001</v>
+      </c>
+      <c r="U26">
+        <v>180</v>
+      </c>
+      <c r="V26">
+        <v>2.8662420000000002</v>
+      </c>
+      <c r="W26">
+        <v>27.577777999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27">
+        <v>123</v>
+      </c>
+      <c r="G27" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27">
+        <v>3132</v>
+      </c>
+      <c r="I27">
+        <v>1.4256070000000001</v>
+      </c>
+      <c r="J27">
+        <v>40.162601629999997</v>
+      </c>
+      <c r="K27">
+        <v>160</v>
+      </c>
+      <c r="L27" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27">
+        <v>4940</v>
+      </c>
+      <c r="N27" t="s">
+        <v>78</v>
+      </c>
+      <c r="O27">
+        <v>4465</v>
+      </c>
+      <c r="P27">
+        <v>1106.382979</v>
+      </c>
+      <c r="Q27">
+        <v>123</v>
+      </c>
+      <c r="S27">
+        <v>40.162602</v>
+      </c>
+      <c r="T27">
+        <v>2.754759</v>
+      </c>
+      <c r="U27">
+        <v>141</v>
+      </c>
+      <c r="V27">
+        <v>3.1578949999999999</v>
+      </c>
+      <c r="W27">
+        <v>35.035460999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28">
+        <v>289</v>
+      </c>
+      <c r="G28" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28">
+        <v>5400</v>
+      </c>
+      <c r="I28">
+        <v>1.7411110000000001</v>
+      </c>
+      <c r="J28">
+        <v>17.19723183</v>
+      </c>
+      <c r="K28">
+        <v>160</v>
+      </c>
+      <c r="L28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28">
+        <v>4970</v>
+      </c>
+      <c r="N28" t="s">
+        <v>80</v>
+      </c>
+      <c r="O28">
+        <v>9402</v>
+      </c>
+      <c r="P28">
+        <v>528.61093400000004</v>
+      </c>
+      <c r="Q28">
+        <v>289</v>
+      </c>
+      <c r="S28">
+        <v>17.197232</v>
+      </c>
+      <c r="T28">
+        <v>3.073814</v>
+      </c>
+      <c r="U28">
+        <v>366</v>
+      </c>
+      <c r="V28">
+        <v>3.8927890000000001</v>
+      </c>
+      <c r="W28">
+        <v>13.579235000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29">
+        <v>92</v>
+      </c>
+      <c r="G29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29">
+        <v>3129</v>
+      </c>
+      <c r="I29">
+        <v>1.4688399999999999</v>
+      </c>
+      <c r="J29">
+        <v>53.782608699999997</v>
+      </c>
+      <c r="K29">
+        <v>160</v>
+      </c>
+      <c r="L29" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29">
+        <v>4948</v>
+      </c>
+      <c r="N29" t="s">
+        <v>80</v>
+      </c>
+      <c r="O29">
+        <v>4596</v>
+      </c>
+      <c r="P29">
+        <v>1076.588338</v>
+      </c>
+      <c r="Q29">
+        <v>92</v>
+      </c>
+      <c r="S29">
+        <v>53.782609000000001</v>
+      </c>
+      <c r="T29">
+        <v>2.001741</v>
+      </c>
+      <c r="U29">
+        <v>123</v>
+      </c>
+      <c r="V29">
+        <v>2.67624</v>
+      </c>
+      <c r="W29">
+        <v>40.227642000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30">
+        <v>352</v>
+      </c>
+      <c r="G30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30">
+        <v>4080</v>
+      </c>
+      <c r="I30">
+        <v>1.939951</v>
+      </c>
+      <c r="J30">
+        <v>14.076704550000001</v>
+      </c>
+      <c r="K30">
+        <v>160</v>
+      </c>
+      <c r="L30" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30">
+        <v>4955</v>
+      </c>
+      <c r="N30" t="s">
+        <v>80</v>
+      </c>
+      <c r="O30">
+        <v>7915</v>
+      </c>
+      <c r="P30">
+        <v>626.02653199999997</v>
+      </c>
+      <c r="Q30">
+        <v>352</v>
+      </c>
+      <c r="S30">
+        <v>14.076705</v>
+      </c>
+      <c r="T30">
+        <v>4.4472519999999998</v>
+      </c>
+      <c r="U30">
+        <v>427</v>
+      </c>
+      <c r="V30">
+        <v>5.3948200000000002</v>
+      </c>
+      <c r="W30">
+        <v>11.604215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31">
+        <v>471</v>
+      </c>
+      <c r="G31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H31">
+        <v>6339</v>
+      </c>
+      <c r="I31">
+        <v>1.785928</v>
+      </c>
+      <c r="J31">
+        <v>12.133757960000001</v>
+      </c>
+      <c r="K31" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>5715</v>
+      </c>
+      <c r="N31" t="s">
+        <v>84</v>
+      </c>
+      <c r="O31">
+        <v>11321</v>
+      </c>
+      <c r="P31">
+        <v>504.81406199999998</v>
+      </c>
+      <c r="Q31">
+        <v>471</v>
+      </c>
+      <c r="S31">
+        <v>12.133758</v>
+      </c>
+      <c r="T31">
+        <v>4.1604099999999997</v>
+      </c>
+      <c r="U31">
+        <v>554</v>
+      </c>
+      <c r="V31">
+        <v>4.893561</v>
+      </c>
+      <c r="W31">
+        <v>10.315884</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <v>537</v>
+      </c>
+      <c r="G32" t="s">
+        <v>41</v>
+      </c>
+      <c r="H32">
+        <v>8756</v>
+      </c>
+      <c r="I32">
+        <v>1.58931</v>
+      </c>
+      <c r="J32">
+        <v>10.338919929999999</v>
+      </c>
+      <c r="K32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>5552</v>
+      </c>
+      <c r="N32" t="s">
+        <v>84</v>
+      </c>
+      <c r="O32">
+        <v>13916</v>
+      </c>
+      <c r="P32">
+        <v>398.96521999999999</v>
+      </c>
+      <c r="Q32">
+        <v>537</v>
+      </c>
+      <c r="S32">
+        <v>10.33892</v>
+      </c>
+      <c r="T32">
+        <v>3.858867</v>
+      </c>
+      <c r="U32">
+        <v>574</v>
+      </c>
+      <c r="V32">
+        <v>4.1247480000000003</v>
+      </c>
+      <c r="W32">
+        <v>9.6724739999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33">
+        <v>170</v>
+      </c>
+      <c r="G33" t="s">
+        <v>41</v>
+      </c>
+      <c r="H33">
+        <v>5329</v>
+      </c>
+      <c r="I33">
+        <v>1.793582</v>
+      </c>
+      <c r="J33">
+        <v>35.123529410000003</v>
+      </c>
+      <c r="K33" t="s">
+        <v>37</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>5971</v>
+      </c>
+      <c r="N33" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33">
+        <v>9558</v>
+      </c>
+      <c r="P33">
+        <v>624.71228299999996</v>
+      </c>
+      <c r="Q33">
+        <v>170</v>
+      </c>
+      <c r="S33">
+        <v>35.123528999999998</v>
+      </c>
+      <c r="T33">
+        <v>1.7786150000000001</v>
+      </c>
+      <c r="U33">
+        <v>283</v>
+      </c>
+      <c r="V33">
+        <v>2.9608699999999999</v>
+      </c>
+      <c r="W33">
+        <v>21.098939999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>200</v>
+      </c>
+      <c r="G34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34">
+        <v>4055</v>
+      </c>
+      <c r="I34">
+        <v>1.7247840000000001</v>
+      </c>
+      <c r="J34">
+        <v>30.295000000000002</v>
+      </c>
+      <c r="K34" t="s">
+        <v>37</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>6059</v>
+      </c>
+      <c r="N34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O34">
+        <v>6994</v>
+      </c>
+      <c r="P34">
+        <v>866.31398300000001</v>
+      </c>
+      <c r="Q34">
+        <v>200</v>
+      </c>
+      <c r="S34">
+        <v>30.295000000000002</v>
+      </c>
+      <c r="T34">
+        <v>2.859594</v>
+      </c>
+      <c r="U34">
+        <v>246</v>
+      </c>
+      <c r="V34">
+        <v>3.5173009999999998</v>
+      </c>
+      <c r="W34">
+        <v>24.630081000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35">
+        <v>635</v>
+      </c>
+      <c r="G35" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35">
+        <v>7089</v>
+      </c>
+      <c r="I35">
+        <v>1.5421069999999999</v>
+      </c>
+      <c r="J35">
+        <v>9.0283464599999999</v>
+      </c>
+      <c r="K35" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>5733</v>
+      </c>
+      <c r="N35" t="s">
+        <v>38</v>
+      </c>
+      <c r="O35">
+        <v>10932</v>
+      </c>
+      <c r="P35">
+        <v>524.42371000000003</v>
+      </c>
+      <c r="Q35">
+        <v>635</v>
+      </c>
+      <c r="S35">
+        <v>9.0283460000000009</v>
+      </c>
+      <c r="T35">
+        <v>5.8086349999999998</v>
+      </c>
+      <c r="U35">
+        <v>695</v>
+      </c>
+      <c r="V35">
+        <v>6.3574830000000002</v>
+      </c>
+      <c r="W35">
+        <v>8.2489209999999993</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36">
+        <v>281</v>
+      </c>
+      <c r="G36" t="s">
+        <v>41</v>
+      </c>
+      <c r="H36">
+        <v>6387</v>
+      </c>
+      <c r="I36">
+        <v>1.7094100000000001</v>
+      </c>
+      <c r="J36">
+        <v>20.772241990000001</v>
+      </c>
+      <c r="K36" t="s">
+        <v>37</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>5837</v>
+      </c>
+      <c r="N36" t="s">
+        <v>38</v>
+      </c>
+      <c r="O36">
+        <v>10918</v>
+      </c>
+      <c r="P36">
+        <v>534.62172599999997</v>
+      </c>
+      <c r="Q36">
+        <v>281</v>
+      </c>
+      <c r="S36">
+        <v>20.772241999999999</v>
+      </c>
+      <c r="T36">
+        <v>2.573731</v>
+      </c>
+      <c r="U36">
+        <v>343</v>
+      </c>
+      <c r="V36">
+        <v>3.1416010000000001</v>
+      </c>
+      <c r="W36">
+        <v>17.017493000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37">
+        <v>281</v>
+      </c>
+      <c r="G37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H37">
+        <v>5220</v>
+      </c>
+      <c r="I37">
+        <v>1.989655</v>
+      </c>
+      <c r="J37">
+        <v>20.96797153</v>
+      </c>
+      <c r="K37" t="s">
+        <v>37</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>5892</v>
+      </c>
+      <c r="N37" t="s">
+        <v>38</v>
+      </c>
+      <c r="O37">
+        <v>10386</v>
+      </c>
+      <c r="P37">
+        <v>567.30213700000002</v>
+      </c>
+      <c r="Q37">
+        <v>281</v>
+      </c>
+      <c r="S37">
+        <v>20.967972</v>
+      </c>
+      <c r="T37">
+        <v>2.705565</v>
+      </c>
+      <c r="U37">
+        <v>373</v>
+      </c>
+      <c r="V37">
+        <v>3.5913729999999999</v>
+      </c>
+      <c r="W37">
+        <v>15.796246999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38">
+        <v>394</v>
+      </c>
+      <c r="G38" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38">
+        <v>6585</v>
+      </c>
+      <c r="I38">
+        <v>1.5148060000000001</v>
+      </c>
+      <c r="J38">
+        <v>14.784263960000001</v>
+      </c>
+      <c r="K38" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>5825</v>
+      </c>
+      <c r="N38" t="s">
+        <v>63</v>
+      </c>
+      <c r="O38">
+        <v>9975</v>
+      </c>
+      <c r="P38">
+        <v>583.95989999999995</v>
+      </c>
+      <c r="Q38">
+        <v>394</v>
+      </c>
+      <c r="S38">
+        <v>14.784264</v>
+      </c>
+      <c r="T38">
+        <v>3.949875</v>
+      </c>
+      <c r="U38">
+        <v>447</v>
+      </c>
+      <c r="V38">
+        <v>4.4812029999999998</v>
+      </c>
+      <c r="W38">
+        <v>13.031319999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39">
+        <v>411</v>
+      </c>
+      <c r="G39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H39">
+        <v>4536</v>
+      </c>
+      <c r="I39">
+        <v>1.6602730000000001</v>
+      </c>
+      <c r="J39">
+        <v>12.012165449999999</v>
+      </c>
+      <c r="K39">
+        <v>160</v>
+      </c>
+      <c r="L39" t="s">
+        <v>30</v>
+      </c>
+      <c r="M39">
+        <v>4937</v>
+      </c>
+      <c r="N39" t="s">
+        <v>52</v>
+      </c>
+      <c r="O39">
+        <v>7531</v>
+      </c>
+      <c r="P39">
+        <v>655.55703100000005</v>
+      </c>
+      <c r="Q39">
+        <v>411</v>
+      </c>
+      <c r="S39">
+        <v>12.012165</v>
+      </c>
+      <c r="T39">
+        <v>5.4574429999999996</v>
+      </c>
+      <c r="U39">
+        <v>462</v>
+      </c>
+      <c r="V39">
+        <v>6.1346429999999996</v>
+      </c>
+      <c r="W39">
+        <v>10.686147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40" t="s">
+        <v>41</v>
+      </c>
+      <c r="H40">
+        <v>184</v>
+      </c>
+      <c r="I40">
+        <v>1.021739</v>
+      </c>
+      <c r="J40">
+        <v>80</v>
+      </c>
+      <c r="K40">
+        <v>650</v>
+      </c>
+      <c r="L40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40">
+        <v>240</v>
+      </c>
+      <c r="N40" t="s">
+        <v>94</v>
+      </c>
+      <c r="O40">
+        <v>188</v>
+      </c>
+      <c r="P40">
+        <v>1276.5957450000001</v>
+      </c>
+      <c r="Q40">
+        <v>3</v>
+      </c>
+      <c r="S40">
+        <v>80</v>
+      </c>
+      <c r="T40">
+        <v>1.595745</v>
+      </c>
+      <c r="U40">
+        <v>3</v>
+      </c>
+      <c r="V40">
+        <v>1.595745</v>
+      </c>
+      <c r="W40">
+        <v>80</v>
+      </c>
+      <c r="X40">
+        <v>3</v>
+      </c>
+      <c r="Y40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41">
+        <v>26</v>
+      </c>
+      <c r="G41" t="s">
+        <v>41</v>
+      </c>
+      <c r="H41">
+        <v>1416</v>
+      </c>
+      <c r="I41">
+        <v>1.1483049999999999</v>
+      </c>
+      <c r="J41">
+        <v>39.46153846</v>
+      </c>
+      <c r="K41">
+        <v>160</v>
+      </c>
+      <c r="L41" t="s">
+        <v>30</v>
+      </c>
+      <c r="M41">
+        <v>1026</v>
+      </c>
+      <c r="N41" t="s">
+        <v>40</v>
+      </c>
+      <c r="O41">
+        <v>1626</v>
+      </c>
+      <c r="P41">
+        <v>630.99630999999999</v>
+      </c>
+      <c r="Q41">
+        <v>26</v>
+      </c>
+      <c r="S41">
+        <v>39.461537999999997</v>
+      </c>
+      <c r="T41">
+        <v>1.599016</v>
+      </c>
+      <c r="U41">
+        <v>31</v>
+      </c>
+      <c r="V41">
+        <v>1.9065190000000001</v>
+      </c>
+      <c r="W41">
+        <v>33.096774000000003</v>
+      </c>
+      <c r="X41">
+        <v>23</v>
+      </c>
+      <c r="Y41">
+        <v>44.608696000000002</v>
       </c>
     </row>
   </sheetData>
